--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:27:45+00:00</t>
+    <t>2025-02-12T10:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedCoverage</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedCoverage</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -918,7 +918,7 @@
     <t>Coverage.subscriber</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient|http://example.org/StructureDefinition/Hauptversicherter)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient|https://elga.moped.at/StructureDefinition/Hauptversicherter)
 </t>
   </si>
   <si>
@@ -1964,7 +1964,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="134.72265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="137.42578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$84</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3206" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:36:14+00:00</t>
+    <t>2025-02-20T20:13:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -655,7 +655,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://tbd.at/VdasId</t>
+    <t>urn:oid:1.2.40.0.10.1.4.3.9.1</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1064,7 +1064,7 @@
     <t>The codes provided on the health card which identify or confirm the specific policy for the insurer.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:type.coding.system}
+    <t xml:space="preserve">value:type.coding}
 </t>
   </si>
   <si>
@@ -1189,6 +1189,12 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://terminology.hl7.org/CodeSystem/coverage-class"/&gt;
+  &lt;code value="group"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -1198,396 +1204,306 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>Coverage.class:Versichertenkategorien.type.coding.id</t>
-  </si>
-  <si>
-    <t>Coverage.class.type.coding.id</t>
-  </si>
-  <si>
-    <t>Coverage.class:Versichertenkategorien.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Coverage.class.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Coverage.class:Versichertenkategorien.type.coding.system</t>
-  </si>
-  <si>
-    <t>Coverage.class.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should be an absolute reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Coverage.class:Versichertenkategorien.type.coding.version</t>
-  </si>
-  <si>
-    <t>Coverage.class.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Coverage.class:Versichertenkategorien.type.coding.code</t>
-  </si>
-  <si>
-    <t>Coverage.class.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cod-1
+    <t>Coverage.class:Versichertenkategorien.type.text</t>
+  </si>
+  <si>
+    <t>Coverage.class.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.value</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.value.id</t>
+  </si>
+  <si>
+    <t>Coverage.class.value.id</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.value.extension</t>
+  </si>
+  <si>
+    <t>Coverage.class.value.extension</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.value.use</t>
+  </si>
+  <si>
+    <t>Coverage.class.value.use</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.value.type</t>
+  </si>
+  <si>
+    <t>Coverage.class.value.type</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.value.system</t>
+  </si>
+  <si>
+    <t>Coverage.class.value.system</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.value.value</t>
+  </si>
+  <si>
+    <t>Coverage.class.value.value</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.value.period</t>
+  </si>
+  <si>
+    <t>Coverage.class.value.period</t>
+  </si>
+  <si>
+    <t>Coverage.class:Versichertenkategorien.value.assigner</t>
+  </si>
+  <si>
+    <t>Coverage.class.value.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Coverage.class:Versichertenkategorien.type.coding.display</t>
-  </si>
-  <si>
-    <t>Coverage.class.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Coverage.class:Versichertenkategorien.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Coverage.class.type.coding.userSelected</t>
+    <t>Coverage.class:Versichertenkategorien.name</t>
+  </si>
+  <si>
+    <t>Coverage.order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positiveInt
+</t>
+  </si>
+  <si>
+    <t>Relative order of the coverage</t>
+  </si>
+  <si>
+    <t>The order of applicability of this coverage relative to other coverages which are currently in force. Note, there may be gaps in the numbering and this does not imply primary, secondary etc. as the specific positioning of coverages depends upon the episode of care. For example; a patient might have (0) auto insurance (1) their own health insurance and (2) spouse's health insurance. When claiming for treatments which were not the result of an auto accident then only coverages (1) and (2) above would be applicatble and would apply in the order specified in parenthesis.</t>
+  </si>
+  <si>
+    <t>Used in managing the coordination of benefits.</t>
+  </si>
+  <si>
+    <t>Coverage.network</t>
+  </si>
+  <si>
+    <t>Insurer network</t>
+  </si>
+  <si>
+    <t>The insurer-specific identifier for the insurer-defined network of providers to which the beneficiary may seek treatment which will be covered at the 'in-network' rate, otherwise 'out of network' terms and conditions apply.</t>
+  </si>
+  <si>
+    <t>Used in referral for treatment and in claims processing.</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary</t>
+  </si>
+  <si>
+    <t>CoPay
+DeductibleExceptions</t>
+  </si>
+  <si>
+    <t>Patient payments for services/products</t>
+  </si>
+  <si>
+    <t>A suite of codes indicating the cost category and associated amount which have been detailed in the policy and may have been  included on the health card.</t>
+  </si>
+  <si>
+    <t>For example by knowing the patient visit co-pay, the provider can collect the amount prior to undertaking treatment.</t>
+  </si>
+  <si>
+    <t>Required by providers to manage financial transaction with the patient.</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.id</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.extension</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.modifierExtension</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.type</t>
+  </si>
+  <si>
+    <t>Cost category</t>
+  </si>
+  <si>
+    <t>The category of patient centric costs associated with treatment.</t>
+  </si>
+  <si>
+    <t>For example visit, specialist visits, emergency, inpatient care, etc.</t>
+  </si>
+  <si>
+    <t>Needed to identify the category associated with the amount for the patient.</t>
+  </si>
+  <si>
+    <t>The types of services to which patient copayments are specified.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.category</t>
+  </si>
+  <si>
+    <t>Benefit classification</t>
+  </si>
+  <si>
+    <t>Code to identify the general type of benefits under which products and services are provided.</t>
+  </si>
+  <si>
+    <t>Examples include Medical Care, Periodontics, Renal Dialysis, Vision Coverage.</t>
+  </si>
+  <si>
+    <t>Needed to convey the category of service or product for which eligibility is sought.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/ex-benefitcategory</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.network</t>
+  </si>
+  <si>
+    <t>In or out of network</t>
+  </si>
+  <si>
+    <t>Is a flag to indicate whether the benefits refer to in-network providers or out-of-network providers.</t>
+  </si>
+  <si>
+    <t>Needed as in or out of network providers are treated differently under the coverage.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/benefit-network</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.unit</t>
+  </si>
+  <si>
+    <t>Individual or family</t>
+  </si>
+  <si>
+    <t>Indicates if the benefits apply to an individual or to the family.</t>
+  </si>
+  <si>
+    <t>Needed for the understanding of the benefits.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/benefit-unit</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.term</t>
+  </si>
+  <si>
+    <t>Annual or lifetime</t>
+  </si>
+  <si>
+    <t>The term or period of the values such as 'maximum lifetime benefit' or 'maximum annual visits'.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/benefit-term</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity {SimpleQuantity}
+Money</t>
+  </si>
+  <si>
+    <t>The amount or percentage due from the beneficiary</t>
+  </si>
+  <si>
+    <t>The amount due from the patient for the cost category.</t>
+  </si>
+  <si>
+    <t>Amount may be expressed as a percentage of the service/product cost or a fixed amount of currency.</t>
+  </si>
+  <si>
+    <t>Needed to identify the amount for the patient associated with the category.</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.exception</t>
+  </si>
+  <si>
+    <t>Exceptions for patient payments</t>
+  </si>
+  <si>
+    <t>A suite of codes indicating exceptions or reductions to patient costs and their effective periods.</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.exception.id</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.exception.extension</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.exception.modifierExtension</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.exception.type</t>
+  </si>
+  <si>
+    <t>Exception category</t>
+  </si>
+  <si>
+    <t>The code for the specific exception.</t>
+  </si>
+  <si>
+    <t>Needed to identify the exception associated with the amount for the patient.</t>
+  </si>
+  <si>
+    <t>The types of exceptions from the part or full value of financial obligations such as copays.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception</t>
+  </si>
+  <si>
+    <t>Coverage.costToBeneficiary.exception.period</t>
+  </si>
+  <si>
+    <t>The effective period of the exception</t>
+  </si>
+  <si>
+    <t>The timeframe the exception is in force.</t>
+  </si>
+  <si>
+    <t>Needed to identify the applicable timeframe for the exception for the correct calculation of patient costs.</t>
+  </si>
+  <si>
+    <t>Coverage.subrogation</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>Coverage.class:Versichertenkategorien.type.text</t>
-  </si>
-  <si>
-    <t>Coverage.class.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>Coverage.class:Versichertenkategorien.value</t>
-  </si>
-  <si>
-    <t>Coverage.class:Versichertenkategorien.name</t>
-  </si>
-  <si>
-    <t>Coverage.order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positiveInt
-</t>
-  </si>
-  <si>
-    <t>Relative order of the coverage</t>
-  </si>
-  <si>
-    <t>The order of applicability of this coverage relative to other coverages which are currently in force. Note, there may be gaps in the numbering and this does not imply primary, secondary etc. as the specific positioning of coverages depends upon the episode of care. For example; a patient might have (0) auto insurance (1) their own health insurance and (2) spouse's health insurance. When claiming for treatments which were not the result of an auto accident then only coverages (1) and (2) above would be applicatble and would apply in the order specified in parenthesis.</t>
-  </si>
-  <si>
-    <t>Used in managing the coordination of benefits.</t>
-  </si>
-  <si>
-    <t>Coverage.network</t>
-  </si>
-  <si>
-    <t>Insurer network</t>
-  </si>
-  <si>
-    <t>The insurer-specific identifier for the insurer-defined network of providers to which the beneficiary may seek treatment which will be covered at the 'in-network' rate, otherwise 'out of network' terms and conditions apply.</t>
-  </si>
-  <si>
-    <t>Used in referral for treatment and in claims processing.</t>
-  </si>
-  <si>
-    <t>D10</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary</t>
-  </si>
-  <si>
-    <t>CoPay
-DeductibleExceptions</t>
-  </si>
-  <si>
-    <t>Patient payments for services/products</t>
-  </si>
-  <si>
-    <t>A suite of codes indicating the cost category and associated amount which have been detailed in the policy and may have been  included on the health card.</t>
-  </si>
-  <si>
-    <t>For example by knowing the patient visit co-pay, the provider can collect the amount prior to undertaking treatment.</t>
-  </si>
-  <si>
-    <t>Required by providers to manage financial transaction with the patient.</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.id</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.extension</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.modifierExtension</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.type</t>
-  </si>
-  <si>
-    <t>Cost category</t>
-  </si>
-  <si>
-    <t>The category of patient centric costs associated with treatment.</t>
-  </si>
-  <si>
-    <t>For example visit, specialist visits, emergency, inpatient care, etc.</t>
-  </si>
-  <si>
-    <t>Needed to identify the category associated with the amount for the patient.</t>
-  </si>
-  <si>
-    <t>The types of services to which patient copayments are specified.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-copay-type</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.category</t>
-  </si>
-  <si>
-    <t>Benefit classification</t>
-  </si>
-  <si>
-    <t>Code to identify the general type of benefits under which products and services are provided.</t>
-  </si>
-  <si>
-    <t>Examples include Medical Care, Periodontics, Renal Dialysis, Vision Coverage.</t>
-  </si>
-  <si>
-    <t>Needed to convey the category of service or product for which eligibility is sought.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/ex-benefitcategory</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.network</t>
-  </si>
-  <si>
-    <t>In or out of network</t>
-  </si>
-  <si>
-    <t>Is a flag to indicate whether the benefits refer to in-network providers or out-of-network providers.</t>
-  </si>
-  <si>
-    <t>Needed as in or out of network providers are treated differently under the coverage.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/benefit-network</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.unit</t>
-  </si>
-  <si>
-    <t>Individual or family</t>
-  </si>
-  <si>
-    <t>Indicates if the benefits apply to an individual or to the family.</t>
-  </si>
-  <si>
-    <t>Needed for the understanding of the benefits.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/benefit-unit</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.term</t>
-  </si>
-  <si>
-    <t>Annual or lifetime</t>
-  </si>
-  <si>
-    <t>The term or period of the values such as 'maximum lifetime benefit' or 'maximum annual visits'.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/benefit-term</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.value[x]</t>
-  </si>
-  <si>
-    <t>Quantity {SimpleQuantity}
-Money</t>
-  </si>
-  <si>
-    <t>The amount or percentage due from the beneficiary</t>
-  </si>
-  <si>
-    <t>The amount due from the patient for the cost category.</t>
-  </si>
-  <si>
-    <t>Amount may be expressed as a percentage of the service/product cost or a fixed amount of currency.</t>
-  </si>
-  <si>
-    <t>Needed to identify the amount for the patient associated with the category.</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.exception</t>
-  </si>
-  <si>
-    <t>Exceptions for patient payments</t>
-  </si>
-  <si>
-    <t>A suite of codes indicating exceptions or reductions to patient costs and their effective periods.</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.exception.id</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.exception.extension</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.exception.modifierExtension</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.exception.type</t>
-  </si>
-  <si>
-    <t>Exception category</t>
-  </si>
-  <si>
-    <t>The code for the specific exception.</t>
-  </si>
-  <si>
-    <t>Needed to identify the exception associated with the amount for the patient.</t>
-  </si>
-  <si>
-    <t>The types of exceptions from the part or full value of financial obligations such as copays.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/coverage-financial-exception</t>
-  </si>
-  <si>
-    <t>Coverage.costToBeneficiary.exception.period</t>
-  </si>
-  <si>
-    <t>The effective period of the exception</t>
-  </si>
-  <si>
-    <t>The timeframe the exception is in force.</t>
-  </si>
-  <si>
-    <t>Needed to identify the applicable timeframe for the exception for the correct calculation of patient costs.</t>
-  </si>
-  <si>
-    <t>Coverage.subrogation</t>
   </si>
   <si>
     <t>Reimbursement to insurer</t>
@@ -1951,10 +1867,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP83"/>
+  <dimension ref="A1:AP84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="61.02734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="54.30859375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="53.57421875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.57421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -1981,7 +1897,7 @@
     <col min="25" max="25" width="144.8984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="56.2734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="25.8515625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -8150,7 +8066,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>80</v>
@@ -8187,7 +8103,7 @@
         <v>20</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>20</v>
+        <v>379</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>20</v>
@@ -8226,7 +8142,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8247,7 +8163,7 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
@@ -8256,15 +8172,15 @@
         <v>20</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8284,19 +8200,23 @@
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>92</v>
+        <v>212</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>166</v>
+        <v>385</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8344,7 +8264,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>168</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8353,10 +8273,10 @@
         <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8365,7 +8285,7 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>170</v>
+        <v>390</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
@@ -8374,26 +8294,26 @@
         <v>20</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>20</v>
+        <v>391</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8402,21 +8322,23 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>139</v>
+        <v>349</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>173</v>
+        <v>350</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -8452,31 +8374,31 @@
         <v>20</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>176</v>
+        <v>348</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8485,24 +8407,24 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>20</v>
+        <v>353</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>20</v>
+        <v>354</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8510,7 +8432,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>90</v>
@@ -8522,23 +8444,19 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>388</v>
+        <v>166</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
       </c>
@@ -8547,7 +8465,7 @@
         <v>20</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>367</v>
+        <v>20</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>20</v>
@@ -8586,7 +8504,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>392</v>
+        <v>168</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8595,10 +8513,10 @@
         <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8607,7 +8525,7 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>393</v>
+        <v>170</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -8616,7 +8534,7 @@
         <v>20</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>394</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -8628,14 +8546,14 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8644,19 +8562,19 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>397</v>
+        <v>139</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>398</v>
+        <v>173</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>399</v>
+        <v>141</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8694,31 +8612,31 @@
         <v>20</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>400</v>
+        <v>176</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8727,7 +8645,7 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>401</v>
+        <v>170</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>20</v>
@@ -8736,15 +8654,15 @@
         <v>20</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>402</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8761,7 +8679,7 @@
         <v>20</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>91</v>
@@ -8770,14 +8688,16 @@
         <v>110</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>405</v>
+        <v>179</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>407</v>
+        <v>182</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8802,13 +8722,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8826,7 +8746,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>408</v>
+        <v>185</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8835,7 +8755,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>409</v>
+        <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -8847,7 +8767,7 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>410</v>
+        <v>186</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>20</v>
@@ -8856,15 +8776,15 @@
         <v>20</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>411</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8887,17 +8807,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>414</v>
+        <v>190</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>416</v>
+        <v>193</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8922,13 +8844,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8946,7 +8868,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>417</v>
+        <v>197</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8955,7 +8877,7 @@
         <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>409</v>
+        <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>102</v>
@@ -8967,7 +8889,7 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>418</v>
+        <v>186</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>20</v>
@@ -8976,15 +8898,15 @@
         <v>20</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>419</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9007,19 +8929,19 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>422</v>
+        <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>423</v>
+        <v>201</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>424</v>
+        <v>202</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>425</v>
+        <v>203</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>426</v>
+        <v>204</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9029,10 +8951,10 @@
         <v>20</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>20</v>
+        <v>367</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>20</v>
@@ -9068,7 +8990,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>427</v>
+        <v>207</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9089,7 +9011,7 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>428</v>
+        <v>208</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>20</v>
@@ -9098,15 +9020,15 @@
         <v>20</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>429</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>431</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9132,17 +9054,15 @@
         <v>212</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>432</v>
+        <v>213</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>433</v>
+        <v>214</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -9154,7 +9074,7 @@
         <v>20</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>20</v>
@@ -9190,7 +9110,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>436</v>
+        <v>217</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9199,7 +9119,7 @@
         <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>102</v>
@@ -9211,7 +9131,7 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>437</v>
+        <v>219</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>20</v>
@@ -9220,15 +9140,15 @@
         <v>20</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>438</v>
+        <v>220</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9236,7 +9156,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>90</v>
@@ -9251,20 +9171,16 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>150</v>
+        <v>223</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>349</v>
+        <v>224</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>20</v>
       </c>
@@ -9312,10 +9228,10 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>348</v>
+        <v>226</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>90</v>
@@ -9333,24 +9249,24 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>355</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>407</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>356</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9373,18 +9289,18 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>212</v>
+        <v>409</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>357</v>
+        <v>232</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>20</v>
       </c>
@@ -9432,7 +9348,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>356</v>
+        <v>235</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9453,24 +9369,24 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>360</v>
+        <v>237</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>356</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9493,17 +9409,17 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>442</v>
+        <v>212</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>443</v>
+        <v>357</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>444</v>
+        <v>358</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>445</v>
+        <v>359</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9552,7 +9468,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>441</v>
+        <v>356</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9576,21 +9492,21 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>20</v>
+        <v>353</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>20</v>
+        <v>354</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>20</v>
+        <v>360</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9613,17 +9529,17 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>212</v>
+        <v>412</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>447</v>
+        <v>413</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>448</v>
+        <v>414</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>449</v>
+        <v>415</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9672,7 +9588,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9696,7 +9612,7 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>450</v>
+        <v>20</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -9707,21 +9623,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>452</v>
+        <v>20</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9730,22 +9646,20 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>254</v>
+        <v>212</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>453</v>
+        <v>417</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9794,13 +9708,13 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
@@ -9818,7 +9732,7 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -9829,21 +9743,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9855,16 +9769,20 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>166</v>
+        <v>423</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
       </c>
@@ -9912,19 +9830,19 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>168</v>
+        <v>421</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -9933,7 +9851,7 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>20</v>
@@ -9947,21 +9865,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -9973,17 +9891,15 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10032,19 +9948,19 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
@@ -10067,14 +9983,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>260</v>
+        <v>137</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10087,26 +10003,24 @@
         <v>20</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>261</v>
+        <v>139</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O68" t="s" s="2">
-        <v>147</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>20</v>
       </c>
@@ -10154,7 +10068,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>263</v>
+        <v>176</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10175,7 +10089,7 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>20</v>
@@ -10189,45 +10103,45 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>461</v>
+        <v>261</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>462</v>
+        <v>262</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>463</v>
+        <v>141</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>464</v>
+        <v>147</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10252,13 +10166,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>465</v>
+        <v>20</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>466</v>
+        <v>20</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -10276,19 +10190,19 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>460</v>
+        <v>263</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
@@ -10297,7 +10211,7 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
@@ -10311,10 +10225,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>467</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>467</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10334,22 +10248,22 @@
         <v>20</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>468</v>
+        <v>431</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>469</v>
+        <v>432</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10374,11 +10288,13 @@
         <v>20</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>473</v>
+        <v>436</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -10396,7 +10312,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>467</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10431,10 +10347,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10460,14 +10376,16 @@
         <v>189</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="O71" t="s" s="2">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10492,11 +10410,11 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -10514,7 +10432,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10549,10 +10467,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>479</v>
+        <v>444</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>479</v>
+        <v>444</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10578,14 +10496,14 @@
         <v>189</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>481</v>
+        <v>446</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>482</v>
+        <v>447</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10610,11 +10528,11 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>483</v>
+        <v>448</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -10632,7 +10550,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>479</v>
+        <v>444</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10667,10 +10585,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>484</v>
+        <v>449</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>484</v>
+        <v>449</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10696,14 +10614,14 @@
         <v>189</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>485</v>
+        <v>450</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>486</v>
+        <v>451</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10728,11 +10646,11 @@
         <v>20</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>487</v>
+        <v>453</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -10750,7 +10668,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>484</v>
+        <v>449</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10785,10 +10703,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>488</v>
+        <v>454</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>488</v>
+        <v>454</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10808,22 +10726,20 @@
         <v>20</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>489</v>
+        <v>189</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>490</v>
+        <v>455</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -10848,13 +10764,11 @@
         <v>20</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>20</v>
+        <v>457</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>20</v>
@@ -10872,7 +10786,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>488</v>
+        <v>454</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10896,21 +10810,21 @@
         <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>494</v>
+        <v>458</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>494</v>
+        <v>458</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10921,7 +10835,7 @@
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
@@ -10930,20 +10844,22 @@
         <v>20</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>254</v>
+        <v>459</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>495</v>
+        <v>460</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="O75" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -10992,13 +10908,13 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>494</v>
+        <v>458</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
@@ -11016,21 +10932,21 @@
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>20</v>
+        <v>353</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>20</v>
+        <v>354</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>20</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>497</v>
+        <v>464</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11041,7 +10957,7 @@
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -11053,16 +10969,18 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>166</v>
+        <v>465</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>167</v>
+        <v>466</v>
       </c>
       <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
       </c>
@@ -11110,19 +11028,19 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>168</v>
+        <v>464</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>20</v>
@@ -11131,7 +11049,7 @@
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>20</v>
@@ -11145,21 +11063,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>498</v>
+        <v>467</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>498</v>
+        <v>467</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -11171,17 +11089,15 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -11230,19 +11146,19 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
@@ -11265,14 +11181,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>499</v>
+        <v>468</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>499</v>
+        <v>468</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>260</v>
+        <v>137</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11285,26 +11201,24 @@
         <v>20</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>261</v>
+        <v>139</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O78" t="s" s="2">
-        <v>147</v>
-      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>20</v>
       </c>
@@ -11352,7 +11266,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>263</v>
+        <v>176</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11373,7 +11287,7 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>20</v>
@@ -11387,43 +11301,45 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>500</v>
+        <v>469</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>500</v>
+        <v>469</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>501</v>
+        <v>261</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O79" t="s" s="2">
-        <v>503</v>
+        <v>147</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11448,13 +11364,13 @@
         <v>20</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>472</v>
+        <v>20</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>504</v>
+        <v>20</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>505</v>
+        <v>20</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>20</v>
@@ -11472,19 +11388,19 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>500</v>
+        <v>263</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>20</v>
@@ -11493,7 +11409,7 @@
         <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>20</v>
@@ -11507,10 +11423,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11518,7 +11434,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>90</v>
@@ -11533,17 +11449,17 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>507</v>
+        <v>471</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>508</v>
+        <v>472</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>509</v>
+        <v>473</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11568,13 +11484,13 @@
         <v>20</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>20</v>
+        <v>442</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>20</v>
+        <v>474</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>20</v>
+        <v>475</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>20</v>
@@ -11592,10 +11508,10 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>90</v>
@@ -11627,10 +11543,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>510</v>
+        <v>476</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>510</v>
+        <v>476</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11650,22 +11566,20 @@
         <v>20</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>422</v>
+        <v>223</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>511</v>
+        <v>477</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>514</v>
+        <v>479</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -11714,7 +11628,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>510</v>
+        <v>476</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11749,10 +11663,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>515</v>
+        <v>480</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>515</v>
+        <v>480</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11763,7 +11677,7 @@
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
@@ -11775,17 +11689,19 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>516</v>
+        <v>481</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>517</v>
+        <v>482</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="O82" t="s" s="2">
-        <v>519</v>
+        <v>485</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -11834,13 +11750,13 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>515</v>
+        <v>480</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
@@ -11855,24 +11771,24 @@
         <v>20</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>520</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>521</v>
+        <v>486</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>521</v>
+        <v>486</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11883,7 +11799,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
@@ -11895,17 +11811,17 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>523</v>
+        <v>488</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>524</v>
+        <v>489</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>525</v>
+        <v>490</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -11954,13 +11870,13 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>521</v>
+        <v>486</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
@@ -11975,20 +11891,140 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>20</v>
+        <v>286</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="AP83" t="s" s="2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP84" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP83">
+  <autoFilter ref="A1:AP84">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11998,7 +12034,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI82">
+  <conditionalFormatting sqref="A2:AI83">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:47:03+00:00</t>
+    <t>2025-03-01T14:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedCoverage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
